--- a/design/ThietKeCoBan_BasicDesign_VN.xlsx
+++ b/design/ThietKeCoBan_BasicDesign_VN.xlsx
@@ -244,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -297,6 +297,8 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -891,7 +893,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -972,7 +973,7 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Đọc song song 200 chunk -&gt; Validate kiểu dữ liệu -&gt; Khử trùng ID -&gt; Lọc TRANG_THAI=1 -&gt; Cách ly dòng lỗi TU_NGAY&gt;DEN_NGAY -&gt; Ghi Silver.</t>
+          <t>Đọc song song 200 chunk -&gt; Validate kiểu dữ liệu -&gt; Khử trùng toàn cục liên chunk (GlobalDedupTracker) -&gt; Giữ TRANG_THAI IN (0,1), cách ly trạng thái lạ -&gt; Xử lý lỗi đảo ngày TU_NGAY&gt;DEN_NGAY theo chế độ Smart Repair (hoán đổi ngày nếu chu kỳ 25..375 ngày và gắn cờ _FLAG_DATE_SWAPPED, ngược lại đưa vào quarantine) -&gt; Bảo toàn: Bronze = Silver + Quarantine + Dedup_Global.</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
@@ -982,7 +983,7 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Dòng lỗi ghi quarantine; &gt; 1% lỗi logic thì dừng batch cảnh báo</t>
+          <t>Dòng lỗi không phục hồi ghi quarantine; &gt; 1% lỗi nghiêm trọng thì dừng batch cảnh báo</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -1024,12 +1025,12 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>Lọc đối tượng tham gia HS/SV mốc T10/2024 -&gt; Lọc người có tham gia bất kỳ khối nào tại T08/2026 -&gt; Anti-join để tìm người dừng hẳn -&gt; Áp dụng Tie-break -&gt; Tổng hợp 63 tỉnh.</t>
+          <t>Lọc thẻ hợp lệ TRANG_THAI=1 -&gt; Xác định đối tượng tham gia HS/SV mốc T10/2024 -&gt; Lọc người có tham gia bất kỳ khối nào tại T08/2026 -&gt; Anti-join để tìm người dừng hẳn -&gt; Áp dụng Tie-break (SV &gt; HS, DEN_NGAY DESC, SO_THE_KCB ASC) -&gt; Tổng hợp 63 tỉnh.</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>Có (Ghi đè phân vùng theo ngày mốc)</t>
+          <t>Có (Ghi đè Atomic Rename theo ngày mốc)</t>
         </is>
       </c>
       <c r="H7" s="19" t="inlineStr">
@@ -1071,12 +1072,12 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>bc_hssv_gian_doan_bhyt.parquet, tk_dbhc_gian_doan.csv, tk_phan_bo_gian_doan.csv</t>
+          <t>bc_hssv_gian_doan_bhyt.parquet, tk_dbhc_hssv_gian_doan_bhyt.csv, tk_phan_bo_gian_doan.csv</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>Lọc người thỏa mãn mốc đầu T10/2024 (HS/SV) và mốc cuối T07/2026 (bất kỳ khối) -&gt; Chạy Interval Merging SQL gộp thẻ chồng lấn/liên tục -&gt; Tính khoảng trống gaps -&gt; Lọc tổng gap &gt;= 90d -&gt; Xuất kết quả.</t>
+          <t>Lọc thẻ TRANG_THAI=1 -&gt; Xác định ứng viên thỏa mãn đồng thời mốc đầu T10/2024 (HS/SV) và mốc cuối T07/2026 (bất kỳ khối) -&gt; Cắt biên vào kỳ [2024-10-01, 2026-07-31] -&gt; Chạy Window Function MAX(den) OVER (...) gộp thẻ chồng lấn/liên tục -&gt; Tính khoảng trống gaps (đầu kỳ, giữa kỳ, cuối kỳ) -&gt; Lọc tổng gap &gt;= 90d -&gt; Xuất kết quả.</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
@@ -1123,12 +1124,12 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>PostgreSQL 16 (HSSV_PERSON_SUMMARY, HSSV_GAP_HISTORY) và Redis Cache</t>
+          <t>PostgreSQL 16 (HSSV_PERSON_SUMMARY, BC_HSSV_GAP_HISTORY, TK_DBHC_HSSV_TONG_HOP) và Redis Cache</t>
         </is>
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>Nạp dữ liệu vào bảng Serving DB bằng COPY/Batch Insert -&gt; Rebuild Index -&gt; Cập nhật bảng tổng hợp 63 tỉnh -&gt; Tự động xóa &amp; nạp lại Cache Redis cho API 004 và 005.</t>
+          <t>Hợp nhất dữ liệu Gold Ý 1 (DUNG_THAM_GIA) và Ý 2 (GIAN_DOAN) nạp vào bảng Serving DB HSSV_PERSON_SUMMARY bằng COPY/Batch Insert -&gt; Rebuild Index (B-Tree, GIN unaccent) -&gt; Cập nhật bảng tổng hợp 63 tỉnh &amp; phân bố -&gt; Tự động xóa &amp; warm-up Cache Redis cho API 004 và 005.</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -1663,7 +1664,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Bảng lưu trữ lịch sử cấp và quản lý thẻ BHYT đã làm sạch của toàn bộ người tham gia</t>
+          <t>Bảng lưu trữ lịch sử cấp và quản lý thẻ BHYT đã làm sạch và gắn cờ kiểm toán của toàn bộ người tham gia</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Lưu trữ định dạng Parquet nén Snappy, phân vùng theo chunk/tỉnh</t>
+          <t>Lưu trữ định dạng Parquet nén Snappy/Zstd, phân vùng theo chunk/tỉnh</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>Danh mục cơ quan BHXH cấp quận/huyện/tỉnh để ánh xạ địa bàn quản lý</t>
+          <t>Danh mục cơ quan BHXH cấp quận/huyện/tỉnh để ánh xạ địa bàn quản lý về 63 tỉnh/TP</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -1808,22 +1808,22 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Danh sách từng cá nhân HSSV dừng tham gia BHYT từ T10/2024 đến T08/2026</t>
+          <t>Danh sách từng cá nhân HSSV dừng tham gia BHYT từ T10/2024 đến T08/2026 (thực nghiệm trên bộ 200M dòng: 848.413 người)</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>750.000</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
+          <t>848.413</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>+50.000/kỳ</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>Lưu trữ Parquet tầng Gold &amp; Bảng Serving DB, đánh index SO_SO_BHXH</t>
+          <t>Lưu trữ Parquet tầng Gold, đồng bộ sang HSSV_PERSON_SUMMARY</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
@@ -1850,22 +1850,22 @@
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>Danh sách cá nhân HSSV vẫn tham gia nhưng có tổng thời gian gián đoạn &gt;= 90 ngày</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>1.150.000</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>+80.000/kỳ</t>
+          <t>Danh sách cá nhân HSSV vẫn tham gia T07/2026 nhưng có tổng thời gian gián đoạn &gt;= 90 ngày (thực nghiệm: ~241.869 người)</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>241.869</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>+30.000/kỳ</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>Lưu trữ Parquet tầng Gold &amp; Bảng Serving DB, đánh index SO_SO_BHXH</t>
+          <t>Lưu trữ Parquet tầng Gold, đồng bộ sang HSSV_PERSON_SUMMARY</t>
         </is>
       </c>
       <c r="H9" s="19" t="inlineStr">
@@ -1892,22 +1892,22 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Lưu chi tiết từng khoảng trống gián đoạn của từng người (từ ngày, đến ngày, số ngày, loại gap)</t>
+          <t>Lưu chi tiết từng khoảng trống gián đoạn của từng người (đợt số, từ ngày, đến ngày, số ngày, phân loại DAU_KY/GIUA_KY/CUOI_KY)</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>3.600.000</t>
+          <t>650.000</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>+200.000/kỳ</t>
+          <t>+80.000/kỳ</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>Lưu trữ Serving DB, quan hệ 1-N với TBL-HSSV-004, index SO_SO_BHXH</t>
+          <t>Lưu trữ Serving DB, quan hệ 1-N với HSSV_PERSON_SUMMARY, index SO_SO_BHXH</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>Bảng số liệu tổng hợp các chỉ tiêu dừng và gián đoạn của 63 tỉnh/thành phố</t>
+          <t>Bảng số liệu tổng hợp các chỉ tiêu dừng (Ý 1) và gián đoạn (Ý 2) của 63 tỉnh/thành phố</t>
         </is>
       </c>
       <c r="E11" s="18" t="inlineStr">
@@ -1979,7 +1979,7 @@
           <t>Bảng tổng hợp số lượng và tỷ lệ % theo 5 khoảng gián đoạn quy chuẩn cho 63 tỉnh và toàn quốc</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>320</t>
         </is>
@@ -2021,7 +2021,7 @@
           <t>Lưu thông tin các yêu cầu xuất file bất đồng bộ, tiến độ, URL tải và thời gian hết hạn</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>50.000</t>
         </is>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>Tự động dọn dẹp các bản ghi quá 30 ngày (BAT-HSSV-005)</t>
+          <t>Tự động dọn dẹp các bản ghi quá 7-30 ngày (BAT-HSSV-005)</t>
         </is>
       </c>
       <c r="H13" s="19" t="inlineStr">
         <is>
-          <t>Hệ thống</t>
+          <t>Phục vụ API 006</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
           <t>Ghi lại nhật ký người dùng nào, lúc nào, tra cứu mã BHXH nào, xuất báo cáo gì</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>1.000.000</t>
         </is>
@@ -2085,14 +2085,46 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="15" t="n"/>
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>TBL-HSSV-010</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>HSSV_PERSON_SUMMARY</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Bảng hợp nhất tra cứu HSSV vi phạm (Serving DB)</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Bảng Serving DB hợp nhất từ Gold Ý 1 (DUNG_THAM_GIA) và Gold Ý 2 (GIAN_DOAN) để phục vụ truy vấn trực tuyến tốc độ cao</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>1.090.282</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>+80.000/kỳ</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>PostgreSQL 16, đánh B-Tree Composite Index và GIN unaccent trên họ tên</t>
+        </is>
+      </c>
+      <c r="H15" s="19" t="inlineStr">
+        <is>
+          <t>Phục vụ API 001, 002, 006</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="n"/>
@@ -2359,7 +2391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2446,7 +2478,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -2638,12 +2669,12 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2658,7 +2689,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2693,7 +2724,7 @@
           <t>SMALLINT</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2753,7 +2784,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2863,7 +2894,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2878,7 +2909,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="13" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2968,12 +2999,12 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2988,7 +3019,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="13" t="inlineStr">
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3023,7 +3054,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3078,12 +3109,12 @@
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3098,14 +3129,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J16" s="13" t="inlineStr">
+      <c r="J16" s="17" t="inlineStr">
         <is>
           <t>FK -&gt; DM_BHXH</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>Cơ quan quản lý tại mốc gốc</t>
+          <t>Cơ quan quản lý tại mốc gốc (tương đương DM_BHXH_ID)</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3191,7 @@
       </c>
       <c r="K17" s="19" t="inlineStr">
         <is>
-          <t>Mã tỉnh phân bổ báo cáo</t>
+          <t>Mã tỉnh phân bổ báo cáo (tương đương MA_TINH)</t>
         </is>
       </c>
     </row>
@@ -3188,12 +3219,12 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3208,7 +3239,7 @@
           <t>'2024-10-01'</t>
         </is>
       </c>
-      <c r="J18" s="13" t="inlineStr">
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3243,7 +3274,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3260,7 +3291,7 @@
       </c>
       <c r="I19" s="19" t="inlineStr">
         <is>
-          <t>'2026-08-31'</t>
+          <t>'2026-08-10'</t>
         </is>
       </c>
       <c r="J19" s="19" t="inlineStr">
@@ -3270,7 +3301,7 @@
       </c>
       <c r="K19" s="19" t="inlineStr">
         <is>
-          <t>Cố định 2026-08-31 theo CV 835</t>
+          <t>Mốc kiểm tra T08/2026 theo CV 835/QLT</t>
         </is>
       </c>
     </row>
@@ -3298,12 +3329,12 @@
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3318,7 +3349,7 @@
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="J20" s="13" t="inlineStr">
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3358,7 +3389,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="G21" s="18" t="inlineStr">
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -3373,7 +3404,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J21" s="18" t="inlineStr">
+      <c r="J21" s="19" t="inlineStr">
         <is>
           <t>PK, B-tree</t>
         </is>
@@ -3413,7 +3444,7 @@
           <t>100</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G22" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3428,7 +3459,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J22" s="13" t="inlineStr">
+      <c r="J22" s="17" t="inlineStr">
         <is>
           <t>GIN unaccent</t>
         </is>
@@ -3463,7 +3494,7 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3518,12 +3549,12 @@
           <t>SMALLINT</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3538,7 +3569,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J24" s="13" t="inlineStr">
+      <c r="J24" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3593,7 +3624,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J25" s="18" t="inlineStr">
+      <c r="J25" s="19" t="inlineStr">
         <is>
           <t>B-tree</t>
         </is>
@@ -3633,7 +3664,7 @@
           <t>255</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="G26" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3648,14 +3679,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J26" s="13" t="inlineStr">
+      <c r="J26" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>Địa chỉ</t>
+          <t>Địa chỉ cư trú</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3774,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="G28" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3758,7 +3789,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J28" s="13" t="inlineStr">
+      <c r="J28" s="17" t="inlineStr">
         <is>
           <t>IDX_GD_KHOI_GOC</t>
         </is>
@@ -3780,22 +3811,22 @@
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>MA_TINH_GOC</t>
+          <t>TU_NGAY_GOC</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>Mã tỉnh quản lý gốc</t>
+          <t>Ngày bắt đầu thẻ gốc</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="F29" s="18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
@@ -3815,12 +3846,12 @@
       </c>
       <c r="J29" s="19" t="inlineStr">
         <is>
-          <t>IDX_GD_TINH_GOC</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K29" s="19" t="inlineStr">
         <is>
-          <t>Mã tỉnh phân bổ báo cáo</t>
+          <t>Ngày bắt đầu thẻ mốc gốc T10/2024</t>
         </is>
       </c>
     </row>
@@ -3835,25 +3866,25 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>SO_THE_KCB_HIEN_TAI</t>
+          <t>DEN_NGAY_GOC</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Mã thẻ mốc hiện tại</t>
+          <t>Ngày kết thúc thẻ gốc</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3868,14 +3899,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J30" s="13" t="inlineStr">
+      <c r="J30" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>Thẻ đại diện T07/2026</t>
+          <t>Ngày kết thúc thẻ mốc gốc T10/2024</t>
         </is>
       </c>
     </row>
@@ -3890,22 +3921,22 @@
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>MA_KHOI_HIEN_TAI</t>
+          <t>DM_BHXH_ID_GOC</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>Khối tham gia hiện tại</t>
+          <t>Cơ quan BHXH gốc</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="F31" s="18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
@@ -3925,12 +3956,12 @@
       </c>
       <c r="J31" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FK -&gt; DM_BHXH</t>
         </is>
       </c>
       <c r="K31" s="19" t="inlineStr">
         <is>
-          <t>HS, SV, DN, GD, TE...</t>
+          <t>Mã cơ quan quản lý tại mốc gốc</t>
         </is>
       </c>
     </row>
@@ -3945,12 +3976,12 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>MA_TINH_HIEN_TAI</t>
+          <t>MA_TINH_GOC</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>Mã tỉnh quản lý hiện tại</t>
+          <t>Mã tỉnh quản lý gốc</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -3963,7 +3994,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3978,14 +4009,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J32" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t>IDX_GD_TINH_GOC</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
-          <t>Mã tỉnh quản lý mốc hiện tại</t>
+          <t>Mã tỉnh phân bổ báo cáo</t>
         </is>
       </c>
     </row>
@@ -4000,22 +4031,22 @@
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>SO_DOT_GIAN_DOAN</t>
+          <t>SO_THE_KCB_HIEN_TAI</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>Số đợt gián đoạn</t>
+          <t>Mã thẻ mốc hiện tại</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="F33" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="G33" s="19" t="inlineStr">
@@ -4040,7 +4071,7 @@
       </c>
       <c r="K33" s="19" t="inlineStr">
         <is>
-          <t>Số lần ngắt quãng không có thẻ</t>
+          <t>Thẻ đại diện T07/2026</t>
         </is>
       </c>
     </row>
@@ -4055,25 +4086,25 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>SO_NGAY_GIAN_DOAN</t>
+          <t>MA_KHOI_HIEN_TAI</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>Tổng số ngày gián đoạn</t>
+          <t>Khối tham gia hiện tại</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="13" t="inlineStr">
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4088,14 +4119,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J34" s="13" t="inlineStr">
-        <is>
-          <t>IDX_GD_DAYS</t>
+      <c r="J34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>Tổng ngày trống cộng dồn (&gt;= 90)</t>
+          <t>HS, SV, DN, GD, TE...</t>
         </is>
       </c>
     </row>
@@ -4110,197 +4141,1698 @@
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
+          <t>TU_NGAY_HIEN_TAI</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>Ngày bắt đầu thẻ hiện tại</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I35" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K35" s="19" t="inlineStr">
+        <is>
+          <t>Ngày bắt đầu thẻ mốc T07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>BC_HSSV_GIAN_DOAN_BHYT</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>DEN_NGAY_HIEN_TAI</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Ngày kết thúc thẻ hiện tại</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Ngày kết thúc thẻ mốc T07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>BC_HSSV_GIAN_DOAN_BHYT</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>DM_BHXH_ID_HIEN_TAI</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>Cơ quan BHXH hiện tại</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I37" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J37" s="19" t="inlineStr">
+        <is>
+          <t>FK -&gt; DM_BHXH</t>
+        </is>
+      </c>
+      <c r="K37" s="19" t="inlineStr">
+        <is>
+          <t>Mã cơ quan quản lý tại mốc T07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>BC_HSSV_GIAN_DOAN_BHYT</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>MA_TINH_HIEN_TAI</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>Mã tỉnh quản lý hiện tại</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>Mã tỉnh quản lý mốc hiện tại</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>BC_HSSV_GIAN_DOAN_BHYT</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>SO_DOT_GIAN_DOAN</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>Số đợt gián đoạn</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I39" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="19" t="inlineStr">
+        <is>
+          <t>Số lần ngắt quãng không có thẻ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>BC_HSSV_GIAN_DOAN_BHYT</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>SO_NGAY_GIAN_DOAN</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Tổng số ngày gián đoạn</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
+        <is>
+          <t>IDX_GD_DAYS</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>Tổng ngày trống cộng dồn (&gt;= 90)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>BC_HSSV_GIAN_DOAN_BHYT</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
           <t>SO_THANG_GIAN_DOAN</t>
         </is>
       </c>
-      <c r="D35" s="19" t="inlineStr">
+      <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Số tháng gián đoạn quy chuẩn</t>
         </is>
       </c>
-      <c r="E35" s="19" t="inlineStr">
+      <c r="E41" s="19" t="inlineStr">
         <is>
           <t>NUMERIC</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
+      <c r="F41" s="18" t="inlineStr">
         <is>
           <t>4,1</t>
         </is>
       </c>
-      <c r="G35" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H35" s="18" t="inlineStr">
+      <c r="G41" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="18" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I35" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J35" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K35" s="19">
+      <c r="I41" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K41" s="19">
         <f> SO_NGAY_GIAN_DOAN / 30.0</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>BC_HSSV_GIAN_DOAN_BHYT</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>NGAY_GOC / NGAY_KIEM_TRA</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>Kỳ tính gián đoạn</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="B42" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>NGAY_GOC</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>Mốc bắt đầu kỳ xét</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="17" t="inlineStr">
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>2024-10-01 / 2026-07-31</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K36" s="13" t="inlineStr">
-        <is>
-          <t>Kỳ xét gián đoạn 669 ngày</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>'2024-10-01'</t>
+        </is>
+      </c>
+      <c r="J42" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>Cố định 2024-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>BC_HSSV_GIAN_DOAN_BHYT</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n">
-        <v>17</v>
-      </c>
-      <c r="C37" s="19" t="inlineStr">
+      <c r="B43" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>NGAY_KIEM_TRA</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Mốc kết thúc kỳ xét</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I43" s="19" t="inlineStr">
+        <is>
+          <t>'2026-07-31'</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" s="19" t="inlineStr">
+        <is>
+          <t>Cố định 2026-07-31 (Kỳ 669 ngày)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>BC_HSSV_GIAN_DOAN_BHYT</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>CREATED_AT</t>
         </is>
       </c>
-      <c r="D37" s="19" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>Thời điểm tạo bản ghi</t>
         </is>
       </c>
-      <c r="E37" s="19" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="F37" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H37" s="18" t="inlineStr">
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I37" s="19" t="inlineStr">
+      <c r="I44" s="13" t="inlineStr">
         <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="J37" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K37" s="19" t="inlineStr">
+      <c r="J44" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
         <is>
           <t>Thời gian ghi bản ghi</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="15" t="n"/>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="15" t="n"/>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
-      <c r="H38" s="15" t="n"/>
-      <c r="I38" s="15" t="n"/>
-      <c r="J38" s="15" t="n"/>
-      <c r="K38" s="15" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="n"/>
-      <c r="B39" s="15" t="n"/>
-      <c r="C39" s="15" t="n"/>
-      <c r="D39" s="15" t="n"/>
-      <c r="E39" s="15" t="n"/>
-      <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
-      <c r="H39" s="15" t="n"/>
-      <c r="I39" s="15" t="n"/>
-      <c r="J39" s="15" t="n"/>
-      <c r="K39" s="15" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="15" t="n"/>
-      <c r="C40" s="15" t="n"/>
-      <c r="D40" s="15" t="n"/>
-      <c r="E40" s="15" t="n"/>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
-      <c r="H40" s="15" t="n"/>
-      <c r="I40" s="15" t="n"/>
-      <c r="J40" s="15" t="n"/>
-      <c r="K40" s="15" t="n"/>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>HSSV_PERSON_SUMMARY</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>SO_SO_BHXH</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>Mã số BHXH</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G45" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I45" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" s="19" t="inlineStr">
+        <is>
+          <t>PK, B-tree</t>
+        </is>
+      </c>
+      <c r="K45" s="19" t="inlineStr">
+        <is>
+          <t>Khóa chính người tham gia (Do ĐK2 của Ý 1 và Ý 2 loại trừ nhau nên mỗi mã số chỉ thuộc 1 tiêu chí)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>HSSV_PERSON_SUMMARY</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>HO_TEN</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>Họ và tên</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="17" t="inlineStr">
+        <is>
+          <t>B-tree</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>Họ và tên có dấu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>HSSV_PERSON_SUMMARY</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>HO_TEN_UNACCENT</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>Họ tên không dấu</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I47" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="19" t="inlineStr">
+        <is>
+          <t>GIN (gin_trgm_ops)</t>
+        </is>
+      </c>
+      <c r="K47" s="19" t="inlineStr">
+        <is>
+          <t>Cột chuẩn hóa không dấu phục vụ tìm kiếm ILIKE nhanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>HSSV_PERSON_SUMMARY</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>NGAY_SINH / GIOI_TINH</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>Ngày sinh &amp; Giới tính</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>DATE / SMALLINT</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>Thông tin nhân thân</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>HSSV_PERSON_SUMMARY</t>
+        </is>
+      </c>
+      <c r="B49" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>SO_CMND / DIA_CHI</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>CCCD &amp; Địa chỉ</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>12 / 255</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="18" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="I49" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t>IDX_CMND</t>
+        </is>
+      </c>
+      <c r="K49" s="19" t="inlineStr">
+        <is>
+          <t>Thông tin định danh phụ</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>HSSV_PERSON_SUMMARY</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>TIEU_CHI</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>Tiêu chí vi phạm CV 835</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J50" s="17" t="inlineStr">
+        <is>
+          <t>IDX_SUMMARY_FILTER</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>DUNG_THAM_GIA (Ý 1) hoặc GIAN_DOAN (Ý 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>HSSV_PERSON_SUMMARY</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>MA_KHOI_GOC / MA_TINH_GOC</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>Khối gốc &amp; Tỉnh gốc</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>10 / 20</t>
+        </is>
+      </c>
+      <c r="G51" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I51" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J51" s="19" t="inlineStr">
+        <is>
+          <t>IDX_SUMMARY_FILTER</t>
+        </is>
+      </c>
+      <c r="K51" s="19" t="inlineStr">
+        <is>
+          <t>Composite Index (MA_TINH_GOC, TIEU_CHI, MA_KHOI_GOC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>HSSV_PERSON_SUMMARY</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>DM_BHXH_ID_GOC</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>Mã cơ quan BHXH gốc</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J52" s="17" t="inlineStr">
+        <is>
+          <t>FK -&gt; DM_BHXH</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>Cơ quan BHXH quản lý tại mốc T10/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>HSSV_PERSON_SUMMARY</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>SO_THE_KCB_GOC / TU_NGAY_GOC / DEN_NGAY_GOC</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>Thông tin thẻ mốc gốc</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>VARCHAR / DATE</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G53" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I53" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J53" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K53" s="19" t="inlineStr">
+        <is>
+          <t>Thẻ đại diện tại mốc gốc T10/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>HSSV_PERSON_SUMMARY</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>SO_THE_KCB_HIEN_TAI / MA_KHOI_HIEN_TAI / TU_NGAY_HIEN_TAI / DEN_NGAY_HIEN_TAI</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>Thông tin thẻ mốc hiện tại</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>VARCHAR / DATE</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>15 / 10</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="17" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="J54" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>Null nếu TIEU_CHI = 'DUNG_THAM_GIA'; có giá trị nếu 'GIAN_DOAN'</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>HSSV_PERSON_SUMMARY</t>
+        </is>
+      </c>
+      <c r="B55" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="C55" s="19" t="inlineStr">
+        <is>
+          <t>SO_DOT_GIAN_DOAN / SO_NGAY_GIAN_DOAN / SO_THANG_GIAN_DOAN</t>
+        </is>
+      </c>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>Chỉ số gián đoạn</t>
+        </is>
+      </c>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>INTEGER / NUMERIC</t>
+        </is>
+      </c>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I55" s="19" t="inlineStr">
+        <is>
+          <t>0 / 0.0</t>
+        </is>
+      </c>
+      <c r="J55" s="19" t="inlineStr">
+        <is>
+          <t>IDX_GD_DAYS</t>
+        </is>
+      </c>
+      <c r="K55" s="19" t="inlineStr">
+        <is>
+          <t>Bằng 0 nếu dừng tham gia; &gt;= 90 ngày nếu gián đoạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>HSSV_PERSON_SUMMARY</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>NGAY_GOC / NGAY_KIEM_TRA / CREATED_AT</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>Mốc thời gian báo cáo</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>DATE / TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="J56" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>Metadata đồng bộ từ tầng Gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>BC_HSSV_GAP_HISTORY</t>
+        </is>
+      </c>
+      <c r="B57" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>ID / SO_SO_BHXH / DOT_NO</t>
+        </is>
+      </c>
+      <c r="D57" s="19" t="inlineStr">
+        <is>
+          <t>Khóa định danh đợt gián đoạn</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>BIGINT / VARCHAR(10) / INT</t>
+        </is>
+      </c>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I57" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J57" s="19" t="inlineStr">
+        <is>
+          <t>PK, IDX_GAP_PERSON</t>
+        </is>
+      </c>
+      <c r="K57" s="19" t="inlineStr">
+        <is>
+          <t>Thứ tự đợt gián đoạn của cá nhân (1..N)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>BC_HSSV_GAP_HISTORY</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>TU_NGAY / DEN_NGAY / SO_NGAY</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>Khoảng thời gian trống</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>DATE / INTEGER</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J58" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>Từ ngày, đến ngày và số ngày trống của đợt</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>BC_HSSV_GAP_HISTORY</t>
+        </is>
+      </c>
+      <c r="B59" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>PHAN_LOAI / GHI_CHU</t>
+        </is>
+      </c>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t>Phân loại đợt gián đoạn</t>
+        </is>
+      </c>
+      <c r="E59" s="19" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>20 / 255</t>
+        </is>
+      </c>
+      <c r="G59" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I59" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J59" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K59" s="19" t="inlineStr">
+        <is>
+          <t>DAU_KY (trước thẻ đầu), GIUA_KY (giữa 2 đoạn), CUOI_KY (sau thẻ cuối)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>TK_DBHC_HSSV_TONG_HOP</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>MA_TINH / TEN_TINH</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>Mã &amp; Tên Tỉnh/TP</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>20 / 200</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H60" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J60" s="17" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>63 Tỉnh/Thành phố trực thuộc TW</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>TK_DBHC_HSSV_TONG_HOP</t>
+        </is>
+      </c>
+      <c r="B61" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" s="19" t="inlineStr">
+        <is>
+          <t>SO_LUONG_HS_DUNG / SO_LUONG_SV_DUNG / TONG_SO_DUNG</t>
+        </is>
+      </c>
+      <c r="D61" s="19" t="inlineStr">
+        <is>
+          <t>Chỉ tiêu dừng tham gia (Ý 1)</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I61" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J61" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K61" s="19" t="inlineStr">
+        <is>
+          <t>Tổng hợp từ BC_HSSV_DUNG_THAM_GIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>TK_DBHC_HSSV_TONG_HOP</t>
+        </is>
+      </c>
+      <c r="B62" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>SO_LUONG_HS_GIAN_DOAN / SO_LUONG_SV_GIAN_DOAN / TONG_SO_GIAN_DOAN / TONG_NGAY_GIAN_DOAN / NGAY_GIAN_DOAN_TRUNG_BINH</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>Chỉ tiêu gián đoạn (Ý 2)</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>BIGINT / NUMERIC</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J62" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>Tổng hợp từ BC_HSSV_GIAN_DOAN_BHYT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="19" t="inlineStr">
+        <is>
+          <t>TK_PHAN_BO_GIAN_DOAN</t>
+        </is>
+      </c>
+      <c r="B63" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>MA_TINH / MA_KHOI / BUCKET_ID</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>Khóa phân bố</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>VARCHAR / INT</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>20 / 10</t>
+        </is>
+      </c>
+      <c r="G63" s="19" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I63" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>PK, IDX_DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="K63" s="19" t="inlineStr">
+        <is>
+          <t>Mã tỉnh ('ALL' hoặc 01..96), Khối ('ALL','HS','SV'), Bucket (1..5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>TK_PHAN_BO_GIAN_DOAN</t>
+        </is>
+      </c>
+      <c r="B64" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>LABEL / MIN_DAYS / MAX_DAYS</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>Mô tả khoảng ngày</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>VARCHAR / INT</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J64" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>5 khoảng: 90-120, 121-180, 181-270, 271-365, &gt;365 ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>TK_PHAN_BO_GIAN_DOAN</t>
+        </is>
+      </c>
+      <c r="B65" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" s="19" t="inlineStr">
+        <is>
+          <t>COUNT_HS / COUNT_SV / TOTAL_COUNT / PERCENTAGE / AVG_GAP_DAYS</t>
+        </is>
+      </c>
+      <c r="D65" s="19" t="inlineStr">
+        <is>
+          <t>Số liệu thống kê bucket</t>
+        </is>
+      </c>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>BIGINT / NUMERIC</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="I65" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J65" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K65" s="19" t="inlineStr">
+        <is>
+          <t>Số lượng HS, SV, Tổng, Tỷ lệ % và Số ngày gián đoạn trung bình</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4400,7 +5932,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -5333,7 +6864,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -6015,7 +7545,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -6369,16 +7898,54 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
+      <c r="A12" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>2026/10/28</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Kỹ sư dữ liệu</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>09 - BAT-001</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Lỗi đảo ngày (TU_NGAY &gt; DEN_NGAY) do nhập liệu có cách ly hết vào Quarantine không?</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>Áp dụng chế độ Smart Repair (Tuần 1 Ngày 5): Nếu độ lệch nằm trong chu kỳ thẻ hợp lệ (25..375 ngày) thì tự động hoán đổi ngày và gắn cờ _FLAG_DATE_SWAPPED = True để tránh Dương tính giả (131 ca); chỉ cách ly vào Quarantine các dòng rác ngoài chu kỳ.</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>2026/10/28</t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>Có (Mục 09)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="n"/>
@@ -6815,7 +8382,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
@@ -6827,12 +8393,12 @@
           <t>Hệ thống Xử lý, Rà soát Dữ liệu Lớn 200M Thẻ BHYT &amp; Cung cấp Cổng Dịch vụ Tra cứu HSSV</t>
         </is>
       </c>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="14" t="n"/>
-      <c r="G5" s="14" t="n"/>
-      <c r="H5" s="14" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="23" t="n"/>
       <c r="I5" s="15" t="n"/>
       <c r="J5" s="15" t="n"/>
     </row>
@@ -6847,12 +8413,12 @@
           <t>Phân hệ Phân tích Dữ liệu Lớn &amp; Cổng Dịch vụ Tra cứu BHYT Học sinh - Sinh viên</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="14" t="n"/>
-      <c r="E6" s="14" t="n"/>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="14" t="n"/>
-      <c r="H6" s="14" t="n"/>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="22" t="n"/>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="23" t="n"/>
       <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="n"/>
     </row>
@@ -6867,12 +8433,12 @@
           <t>Thiết kế cơ bản (Basic Design)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
-      <c r="H7" s="14" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="23" t="n"/>
       <c r="I7" s="15" t="n"/>
       <c r="J7" s="15" t="n"/>
     </row>
@@ -6887,12 +8453,12 @@
           <t>HSSV-BD-001</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="23" t="n"/>
       <c r="I8" s="15" t="n"/>
       <c r="J8" s="15" t="n"/>
     </row>
@@ -6907,12 +8473,12 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="23" t="n"/>
       <c r="I9" s="15" t="n"/>
       <c r="J9" s="15" t="n"/>
     </row>
@@ -6927,12 +8493,12 @@
           <t>Nhóm Kỹ sư Dữ liệu &amp; Hệ thống (Pair Programming)</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="14" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="23" t="n"/>
       <c r="I10" s="15" t="n"/>
       <c r="J10" s="15" t="n"/>
     </row>
@@ -6947,12 +8513,12 @@
           <t>Tech Lead / Solution Architect</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
-      <c r="H11" s="14" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="23" t="n"/>
       <c r="I11" s="15" t="n"/>
       <c r="J11" s="15" t="n"/>
     </row>
@@ -6967,12 +8533,12 @@
           <t>Trưởng ban Quản lý Thu &amp; Khai thác BHYT (BHXH Việt Nam)</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="14" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="23" t="n"/>
       <c r="I12" s="15" t="n"/>
       <c r="J12" s="15" t="n"/>
     </row>
@@ -6987,12 +8553,12 @@
           <t>2026/10/28</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-      <c r="H13" s="14" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="23" t="n"/>
       <c r="I13" s="15" t="n"/>
       <c r="J13" s="15" t="n"/>
     </row>
@@ -7007,12 +8573,12 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="23" t="n"/>
       <c r="I14" s="15" t="n"/>
       <c r="J14" s="15" t="n"/>
     </row>
@@ -7027,12 +8593,12 @@
           <t>Công văn số 835/QLT ngày 10/08/2026 của BHXH VN; Đặc tả nghiệp vụ Tuần 1 (Ý 1 - Dừng tham gia) &amp; Tuần 2 (Ý 2 - Gián đoạn &gt;= 3 tháng)</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-      <c r="H15" s="14" t="n"/>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="23" t="n"/>
       <c r="I15" s="15" t="n"/>
       <c r="J15" s="15" t="n"/>
     </row>
@@ -7345,9 +8911,9 @@
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="B11:H11"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B10:H10"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B5:H5"/>
   </mergeCells>
@@ -7445,7 +9011,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -7523,13 +9088,41 @@
       <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n"/>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>2026/10/28</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>08_DinhNghiaAPI, 09_DSBatch, 10_DSBang, 11_DinhNghiaBang, 14_QA</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Đồng bộ 100% logic Global Dedup, Smart Repair lỗi đảo ngày (Tuần 1), chuẩn hóa đủ 24 cột BC_HSSV_GIAN_DOAN_BHYT (Tuần 2), bổ sung định nghĩa bảng Serving DB HSSV_PERSON_SUMMARY và cập nhật số liệu thực nghiệm 200M dòng</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Đối soát và chuẩn hóa thiết kế với bài làm Tuần 1 &amp; Tuần 2</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Nhóm Kỹ sư</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
       <c r="H7" s="15" t="n"/>
     </row>
     <row r="8">
@@ -7961,7 +9554,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
@@ -7973,12 +9565,12 @@
           <t>Xây dựng hệ thống hoàn chỉnh xử lý 200 triệu dòng thẻ BHYT theo kiến trúc Medallion Lakehouse nhằm phát hiện chính xác HSSV dừng tham gia hoặc gián đoạn &gt;= 3 tháng theo Công văn 835/QLT; đồng thời cung cấp hệ sinh thái 6 RESTful API phục vụ tra cứu trực tuyến, thống kê 63 tỉnh/thành phố và xuất báo cáo tốc độ cao.</t>
         </is>
       </c>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="14" t="n"/>
-      <c r="G5" s="14" t="n"/>
-      <c r="H5" s="14" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="23" t="n"/>
       <c r="I5" s="15" t="n"/>
       <c r="J5" s="15" t="n"/>
     </row>
@@ -7999,12 +9591,12 @@
 7. F-HSSV-007: Pipeline ETL Big Data (Bronze -&gt; Silver -&gt; Gold) xử lý 200M bản ghi thẻ BHYT bằng DuckDB SQL &amp; Polars.</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="14" t="n"/>
-      <c r="E6" s="14" t="n"/>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="14" t="n"/>
-      <c r="H6" s="14" t="n"/>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="22" t="n"/>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="23" t="n"/>
       <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="n"/>
     </row>
@@ -8021,12 +9613,12 @@
 3. Quản lý thu tiền đóng BHYT và kế toán thanh toán.</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
-      <c r="H7" s="14" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="23" t="n"/>
       <c r="I7" s="15" t="n"/>
       <c r="J7" s="15" t="n"/>
     </row>
@@ -8043,12 +9635,12 @@
 3. ACT-03: Kỹ sư vận hành / Batch Scheduler (vận hành và giám sát pipeline xử lý dữ liệu lớn định kỳ).</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="23" t="n"/>
       <c r="I8" s="15" t="n"/>
       <c r="J8" s="15" t="n"/>
     </row>
@@ -8063,12 +9655,12 @@
           <t>Web UI (React 18) &amp; Hệ thống ngoài -&gt; API Gateway (Nginx/Kong) -&gt; Backend Service (FastAPI / Spring Boot 3) -&gt; Redis Cache (Dashboard 63 tỉnh, phân bố) &amp; PostgreSQL 16 Serving DB (Bảng tổng hợp, index tối ưu) &lt;- Pipeline ETL Engine (DuckDB / Polars) &lt;- Lakehouse Storage (Parquet Bronze -&gt; Silver -&gt; Gold: 200M thẻ).</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="23" t="n"/>
       <c r="I9" s="15" t="n"/>
       <c r="J9" s="15" t="n"/>
     </row>
@@ -8083,12 +9675,12 @@
           <t>Backend: Python 3.12, FastAPI 0.115+, DuckDB 1.1+, Polars 1.12+, PyArrow 17+; DB: PostgreSQL 16, Redis 7.2; Frontend: React 18, TailwindCSS/Vanilla, ECharts; Storage: MinIO/S3 (chứa file export); Batch: Airflow/Celery Worker.</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="14" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="23" t="n"/>
       <c r="I10" s="15" t="n"/>
       <c r="J10" s="15" t="n"/>
     </row>
@@ -8107,12 +9699,12 @@
 5. Kỳ tính gián đoạn: [2024-10-01, 2026-07-31] (669 ngày). Ngưỡng gián đoạn &gt;= 90 ngày.</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
-      <c r="H11" s="14" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="23" t="n"/>
       <c r="I11" s="15" t="n"/>
       <c r="J11" s="15" t="n"/>
     </row>
@@ -8132,12 +9724,12 @@
 Tie-breaking: Quy tắc phân giải đa thẻ trùng mốc (ưu tiên SV &gt; HS, DEN_NGAY lớn nhất, SO_THE_KCB).</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="14" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="23" t="n"/>
       <c r="I12" s="15" t="n"/>
       <c r="J12" s="15" t="n"/>
     </row>
@@ -8483,9 +10075,9 @@
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="B11:H11"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B10:H10"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B5:H5"/>
   </mergeCells>
@@ -8585,7 +10177,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -9369,7 +10960,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -9993,7 +11583,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -11659,7 +13248,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -12473,7 +14061,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -12572,7 +14159,7 @@
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>BC_HSSV.MA_TINH_GOC</t>
+          <t>HSSV_PERSON_SUMMARY.MA_TINH_GOC</t>
         </is>
       </c>
     </row>
@@ -12622,7 +14209,7 @@
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t>BC_HSSV.MA_KHOI_GOC</t>
+          <t>HSSV_PERSON_SUMMARY.MA_KHOI_GOC</t>
         </is>
       </c>
     </row>
@@ -12672,7 +14259,7 @@
       </c>
       <c r="J8" s="13" t="inlineStr">
         <is>
-          <t>BC_HSSV.TIEU_CHI</t>
+          <t>HSSV_PERSON_SUMMARY.TIEU_CHI</t>
         </is>
       </c>
     </row>
@@ -12772,7 +14359,7 @@
       </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
-          <t>BC_HSSV.SO_NGAY_GIAN_DOAN</t>
+          <t>HSSV_PERSON_SUMMARY.SO_NGAY_GIAN_DOAN</t>
         </is>
       </c>
     </row>
@@ -12822,7 +14409,7 @@
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t>BC_HSSV.SO_NGAY_GIAN_DOAN</t>
+          <t>HSSV_PERSON_SUMMARY.SO_NGAY_GIAN_DOAN</t>
         </is>
       </c>
     </row>
@@ -13222,7 +14809,7 @@
       </c>
       <c r="J19" s="19" t="inlineStr">
         <is>
-          <t>BC_HSSV.SO_SO_BHXH</t>
+          <t>HSSV_PERSON_SUMMARY.SO_SO_BHXH</t>
         </is>
       </c>
     </row>
@@ -13272,7 +14859,7 @@
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
-          <t>BC_HSSV.HO_TEN</t>
+          <t>HSSV_PERSON_SUMMARY.HO_TEN</t>
         </is>
       </c>
     </row>
@@ -13322,7 +14909,7 @@
       </c>
       <c r="J21" s="19" t="inlineStr">
         <is>
-          <t>BC_HSSV.NGAY_SINH, GIOI_TINH</t>
+          <t>HSSV_PERSON_SUMMARY.NGAY_SINH, GIOI_TINH</t>
         </is>
       </c>
     </row>
@@ -13372,7 +14959,7 @@
       </c>
       <c r="J22" s="13" t="inlineStr">
         <is>
-          <t>BC_HSSV.MA_KHOI_GOC, MA_TINH_GOC</t>
+          <t>HSSV_PERSON_SUMMARY.MA_KHOI_GOC, MA_TINH_GOC</t>
         </is>
       </c>
     </row>
@@ -13422,7 +15009,7 @@
       </c>
       <c r="J23" s="19" t="inlineStr">
         <is>
-          <t>BC_HSSV.TIEU_CHI</t>
+          <t>HSSV_PERSON_SUMMARY.TIEU_CHI</t>
         </is>
       </c>
     </row>
@@ -13472,7 +15059,7 @@
       </c>
       <c r="J24" s="13" t="inlineStr">
         <is>
-          <t>BC_HSSV.SO_NGAY_GIAN_DOAN</t>
+          <t>HSSV_PERSON_SUMMARY.SO_NGAY_GIAN_DOAN</t>
         </is>
       </c>
     </row>
@@ -13572,7 +15159,7 @@
       </c>
       <c r="J26" s="13" t="inlineStr">
         <is>
-          <t>BC_HSSV.SO_SO_BHXH</t>
+          <t>HSSV_PERSON_SUMMARY.SO_SO_BHXH</t>
         </is>
       </c>
     </row>
@@ -13622,7 +15209,7 @@
       </c>
       <c r="J27" s="19" t="inlineStr">
         <is>
-          <t>BC_HSSV.SO_SO_BHXH</t>
+          <t>HSSV_PERSON_SUMMARY.SO_SO_BHXH</t>
         </is>
       </c>
     </row>
@@ -13672,7 +15259,7 @@
       </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>BC_HSSV.HO_TEN</t>
+          <t>HSSV_PERSON_SUMMARY.HO_TEN</t>
         </is>
       </c>
     </row>
@@ -13722,7 +15309,7 @@
       </c>
       <c r="J29" s="19" t="inlineStr">
         <is>
-          <t>BC_HSSV.NGAY_SINH, GIOI_TINH</t>
+          <t>HSSV_PERSON_SUMMARY.NGAY_SINH, GIOI_TINH</t>
         </is>
       </c>
     </row>
@@ -13772,7 +15359,7 @@
       </c>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>BC_HSSV.SO_CMND, DIA_CHI</t>
+          <t>HSSV_PERSON_SUMMARY.SO_CMND, DIA_CHI</t>
         </is>
       </c>
     </row>
@@ -13822,7 +15409,7 @@
       </c>
       <c r="J31" s="19" t="inlineStr">
         <is>
-          <t>BC_HSSV.TIEU_CHI</t>
+          <t>HSSV_PERSON_SUMMARY.TIEU_CHI</t>
         </is>
       </c>
     </row>
@@ -13972,7 +15559,7 @@
       </c>
       <c r="J34" s="13" t="inlineStr">
         <is>
-          <t>BC_HSSV.SO_NGAY_GIAN_DOAN</t>
+          <t>HSSV_PERSON_SUMMARY.SO_NGAY_GIAN_DOAN</t>
         </is>
       </c>
     </row>
@@ -14022,7 +15609,7 @@
       </c>
       <c r="J35" s="19" t="inlineStr">
         <is>
-          <t>BC_HSSV.SO_DOT_GIAN_DOAN</t>
+          <t>HSSV_PERSON_SUMMARY.SO_DOT_GIAN_DOAN</t>
         </is>
       </c>
     </row>
@@ -14122,7 +15709,7 @@
       </c>
       <c r="J37" s="19" t="inlineStr">
         <is>
-          <t>BC_HSSV.SO_SO_BHXH</t>
+          <t>HSSV_PERSON_SUMMARY.SO_SO_BHXH</t>
         </is>
       </c>
     </row>
